--- a/exports/НИЦ Эколог — контент сайта.xlsx
+++ b/exports/НИЦ Эколог — контент сайта.xlsx
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2-ТП (воздух), 2-ТП (водхоз), 2-ТП (отходы), 2-ТП (рекультивация) — подготовка и сдача.</t>
+          <t>2-ТП (воздух), 2-ТП (водхоз), 2-ТП (отходы), 2-ТП (рекультивация) — подготовка и сдача отчётов в личном кабинете природопользователя.</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
@@ -2899,9 +2899,17 @@
           <t>2-ТП (воздух), 2-ТП (водхоз), 2-ТП (отходы), 2-ТП (рекультивация) — подготовка и сдача отчетов самостоятельно в личном кабинете Природопользователя</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>2-ТП (воздух), 2-ТП (водхоз), 2-ТП (отходы), 2-ТП (рекультивация) — подготовка и сдача отчетов  в личном кабинете Природопользователя</t>
+        </is>
+      </c>
       <c r="I72" s="4" t="inlineStr"/>
-      <c r="J72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -10535,14 +10543,22 @@
       </c>
       <c r="E304" s="4" t="inlineStr">
         <is>
-          <t>Расчёт нормативов образования для каждого вида отходов</t>
+          <t>Выполнение лабораторных исследований по определению состава отходов и разработка паспортов для отходов I–IV класса опасности</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr"/>
       <c r="G304" s="4" t="inlineStr"/>
-      <c r="H304" s="4" t="inlineStr"/>
+      <c r="H304" s="4" t="inlineStr">
+        <is>
+          <t>Поменять шаг 2 и 3 местами</t>
+        </is>
+      </c>
       <c r="I304" s="4" t="inlineStr"/>
-      <c r="J304" s="4" t="inlineStr"/>
+      <c r="J304" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
@@ -10567,14 +10583,22 @@
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>Паспортизация отходов I–IV классов опасности</t>
+          <t>Расчёт нормативов образования для каждого вида отходов</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr"/>
       <c r="G305" s="4" t="inlineStr"/>
-      <c r="H305" s="4" t="inlineStr"/>
+      <c r="H305" s="4" t="inlineStr">
+        <is>
+          <t>Выполнение лабораторных исследований по определению состава отходов и разработка паспортов для отходов I-IV класса опасности</t>
+        </is>
+      </c>
       <c r="I305" s="4" t="inlineStr"/>
-      <c r="J305" s="4" t="inlineStr"/>
+      <c r="J305" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
@@ -10599,14 +10623,22 @@
       </c>
       <c r="E306" s="4" t="inlineStr">
         <is>
-          <t>Подготовка и подача документов на лимиты</t>
+          <t>Согласование ПНООЛР с заказчиком</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr"/>
       <c r="G306" s="4" t="inlineStr"/>
-      <c r="H306" s="4" t="inlineStr"/>
+      <c r="H306" s="4" t="inlineStr">
+        <is>
+          <t>согласование ПНООЛР с Заказчиком</t>
+        </is>
+      </c>
       <c r="I306" s="4" t="inlineStr"/>
-      <c r="J306" s="4" t="inlineStr"/>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
@@ -10631,14 +10663,22 @@
       </c>
       <c r="E307" s="4" t="inlineStr">
         <is>
-          <t>Сопровождение рассмотрения в Росприроднадзоре</t>
+          <t>[удалено]</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr"/>
       <c r="G307" s="4" t="inlineStr"/>
-      <c r="H307" s="4" t="inlineStr"/>
+      <c r="H307" s="4" t="inlineStr">
+        <is>
+          <t>удалить</t>
+        </is>
+      </c>
       <c r="I307" s="4" t="inlineStr"/>
-      <c r="J307" s="4" t="inlineStr"/>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
@@ -10855,14 +10895,22 @@
       </c>
       <c r="E314" s="4" t="inlineStr">
         <is>
-          <t>Установление границ СЗЗ — от расчётов до внесения в ЕГРН. Натурные измерения выполняет наша лаборатория, поэтому проект не зависает на этапе подтверждения границ.</t>
+          <t>Установление границ СЗЗ — от расчётов до внесения в ЕГРН. Натурные измерения выполняет наша лаборатория, поэтому сроки разработки проекта СЗЗ сведены к минимуму.</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr"/>
       <c r="G314" s="4" t="inlineStr"/>
-      <c r="H314" s="4" t="inlineStr"/>
+      <c r="H314" s="4" t="inlineStr">
+        <is>
+          <t>Установление границ СЗЗ — от расчётов до внесения в ЕГРН. Натурные измерения выполняет наша лаборатория, поэтому сроки разработки проекта СЗЗ сведены к минимуму</t>
+        </is>
+      </c>
       <c r="I314" s="4" t="inlineStr"/>
-      <c r="J314" s="4" t="inlineStr"/>
+      <c r="J314" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
@@ -10919,14 +10967,22 @@
       </c>
       <c r="E316" s="4" t="inlineStr">
         <is>
-          <t>объекты I–V классов опасности</t>
+          <t>собственнику или арендатору земельного участка, на котором осуществляется деятельность, связанная с образованием выбросов загрязняющих веществ или имеющая источники физического воздействия</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr"/>
       <c r="G316" s="4" t="inlineStr"/>
-      <c r="H316" s="4" t="inlineStr"/>
+      <c r="H316" s="4" t="inlineStr">
+        <is>
+          <t>собственнику или арендатору земельного участка, но котором осуществляться деятельность, связанная с образованием выбросов загрязняющих веществ или имеющая источники физического воздействия</t>
+        </is>
+      </c>
       <c r="I316" s="4" t="inlineStr"/>
-      <c r="J316" s="4" t="inlineStr"/>
+      <c r="J316" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
@@ -10983,14 +11039,22 @@
       </c>
       <c r="E318" s="4" t="inlineStr">
         <is>
-          <t>Оценка достаточности расчётной санитарно-защитной зоны</t>
+          <t>Расчёты выбросов и рассеивания загрязняющих веществ в атмосферном воздухе, а также оценка акустического воздействия</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr"/>
       <c r="G318" s="4" t="inlineStr"/>
-      <c r="H318" s="4" t="inlineStr"/>
+      <c r="H318" s="4" t="inlineStr">
+        <is>
+          <t>шаг 2 и 1 поменять местами</t>
+        </is>
+      </c>
       <c r="I318" s="4" t="inlineStr"/>
-      <c r="J318" s="4" t="inlineStr"/>
+      <c r="J318" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
@@ -11015,14 +11079,22 @@
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
-          <t>Расчёты рассеивания выбросов и акустического воздействия</t>
+          <t>Оценка достаточности расчётной санитарно-защитной зоны</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr"/>
       <c r="G319" s="4" t="inlineStr"/>
-      <c r="H319" s="4" t="inlineStr"/>
+      <c r="H319" s="4" t="inlineStr">
+        <is>
+          <t>Расчёты выбросов и рассеивания  загрязняющих веществ в атмосферном воздухе, а также оценка акустического воздействия</t>
+        </is>
+      </c>
       <c r="I319" s="4" t="inlineStr"/>
-      <c r="J319" s="4" t="inlineStr"/>
+      <c r="J319" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
@@ -11047,14 +11119,22 @@
       </c>
       <c r="E320" s="4" t="inlineStr">
         <is>
-          <t>Натурные измерения на границе СЗЗ силами «Аналитик Лаб»</t>
+          <t>Натурные измерения на границе СЗЗ силами ООО «Аналитик Лаб»</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr"/>
       <c r="G320" s="4" t="inlineStr"/>
-      <c r="H320" s="4" t="inlineStr"/>
+      <c r="H320" s="4" t="inlineStr">
+        <is>
+          <t>Натурные измерения на границе СЗЗ силами ООО «Аналитик Лаб»</t>
+        </is>
+      </c>
       <c r="I320" s="4" t="inlineStr"/>
-      <c r="J320" s="4" t="inlineStr"/>
+      <c r="J320" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
@@ -11079,14 +11159,22 @@
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
-          <t>Санитарно-эпидемиологическая экспертиза и Роспотребнадзор</t>
+          <t>Санитарно-эпидемиологическая экспертиза проектной документации</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr"/>
       <c r="G321" s="4" t="inlineStr"/>
-      <c r="H321" s="4" t="inlineStr"/>
+      <c r="H321" s="4" t="inlineStr">
+        <is>
+          <t>Санитарно-эпидемиологическая экспертиза проектной документации</t>
+        </is>
+      </c>
       <c r="I321" s="4" t="inlineStr"/>
-      <c r="J321" s="4" t="inlineStr"/>
+      <c r="J321" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
@@ -11111,14 +11199,22 @@
       </c>
       <c r="E322" s="4" t="inlineStr">
         <is>
-          <t>Сопровождение внесения границ в ЕГРН</t>
+          <t>Согласование проектной документации в Роспотребнадзоре и внесение границ в ЕГРН</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr"/>
       <c r="G322" s="4" t="inlineStr"/>
-      <c r="H322" s="4" t="inlineStr"/>
+      <c r="H322" s="4" t="inlineStr">
+        <is>
+          <t>Согласование проектной документации в Роспотребнадзоре и внесение границ в ЕГРН</t>
+        </is>
+      </c>
       <c r="I322" s="4" t="inlineStr"/>
-      <c r="J322" s="4" t="inlineStr"/>
+      <c r="J322" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
@@ -11943,14 +12039,22 @@
       </c>
       <c r="E348" s="4" t="inlineStr">
         <is>
-          <t>Оценка фонового состояния территории</t>
+          <t>Оценка существующего положения компонентов природной среды</t>
         </is>
       </c>
       <c r="F348" s="4" t="inlineStr"/>
       <c r="G348" s="4" t="inlineStr"/>
-      <c r="H348" s="4" t="inlineStr"/>
+      <c r="H348" s="4" t="inlineStr">
+        <is>
+          <t>Оценка существующего положения компонентов природной среды</t>
+        </is>
+      </c>
       <c r="I348" s="4" t="inlineStr"/>
-      <c r="J348" s="4" t="inlineStr"/>
+      <c r="J348" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
@@ -11975,14 +12079,22 @@
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
-          <t>Прогноз воздействия по всем компонентам среды</t>
+          <t>Проработка альтернативных вариантов реализации</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr"/>
       <c r="G349" s="4" t="inlineStr"/>
-      <c r="H349" s="4" t="inlineStr"/>
+      <c r="H349" s="4" t="inlineStr">
+        <is>
+          <t>шаг 3 и 2 заменить местами</t>
+        </is>
+      </c>
       <c r="I349" s="4" t="inlineStr"/>
-      <c r="J349" s="4" t="inlineStr"/>
+      <c r="J349" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
@@ -12007,14 +12119,22 @@
       </c>
       <c r="E350" s="4" t="inlineStr">
         <is>
-          <t>Проработка альтернативных вариантов реализации</t>
+          <t>Оценка воздействия проектируемого объекта на все компоненты окружающей среды</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr"/>
       <c r="G350" s="4" t="inlineStr"/>
-      <c r="H350" s="4" t="inlineStr"/>
+      <c r="H350" s="4" t="inlineStr">
+        <is>
+          <t>Оценка воздействия проектируемого объекта на все компоненты окружающей среды</t>
+        </is>
+      </c>
       <c r="I350" s="4" t="inlineStr"/>
-      <c r="J350" s="4" t="inlineStr"/>
+      <c r="J350" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
@@ -12039,14 +12159,22 @@
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
-          <t>Организация и сопровождение общественных обсуждений</t>
+          <t>Организация и сопровождение общественных обсуждений материалов ОВОС</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr"/>
       <c r="G351" s="4" t="inlineStr"/>
-      <c r="H351" s="4" t="inlineStr"/>
+      <c r="H351" s="4" t="inlineStr">
+        <is>
+          <t>Организация и сопровождение общественных обсуждений материалов ОВОС</t>
+        </is>
+      </c>
       <c r="I351" s="4" t="inlineStr"/>
-      <c r="J351" s="4" t="inlineStr"/>
+      <c r="J351" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
@@ -12071,14 +12199,22 @@
       </c>
       <c r="E352" s="4" t="inlineStr">
         <is>
-          <t>Подготовка материалов к экологической экспертизе</t>
+          <t>Подготовка проектной документации к экологической экспертизе</t>
         </is>
       </c>
       <c r="F352" s="4" t="inlineStr"/>
       <c r="G352" s="4" t="inlineStr"/>
-      <c r="H352" s="4" t="inlineStr"/>
+      <c r="H352" s="4" t="inlineStr">
+        <is>
+          <t>Подготовка проектной документации к экологической экспертизе</t>
+        </is>
+      </c>
       <c r="I352" s="4" t="inlineStr"/>
-      <c r="J352" s="4" t="inlineStr"/>
+      <c r="J352" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
@@ -12295,14 +12431,22 @@
       </c>
       <c r="E359" s="4" t="inlineStr">
         <is>
-          <t>Программа ПЭК и её исполнение: что, где и как часто измерять — и сами измерения силами нашей аккредитованной лаборатории.</t>
+          <t>Программа ПЭК и её исполнение: что, где и как часто контролировать. Измерения могут быть выполнены силами нашей аккредитованной лаборатории в полном объёме по всем компонентам окружающей среды.</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr"/>
       <c r="G359" s="4" t="inlineStr"/>
-      <c r="H359" s="4" t="inlineStr"/>
+      <c r="H359" s="4" t="inlineStr">
+        <is>
+          <t>Программа ПЭК и её исполнение: что, где и как часто контролировать. Измерения могут быть выполнены силами нашей аккредитованной лаборатории в полном объекме по всем компонентам окружающей среды</t>
+        </is>
+      </c>
       <c r="I359" s="4" t="inlineStr"/>
-      <c r="J359" s="4" t="inlineStr"/>
+      <c r="J359" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
@@ -12391,14 +12535,22 @@
       </c>
       <c r="E362" s="4" t="inlineStr">
         <is>
-          <t>Утверждённая программа ПЭК и ежегодные отчёты, принимаемые без замечаний. Все измерения — по графику, протоколы — в срок.</t>
+          <t>Утверждённая программа ПЭК и ежегодные отчёты. Все измерения выполнены согласно утверждённому графику, протоколы — в чётко установленный срок.</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr"/>
       <c r="G362" s="4" t="inlineStr"/>
-      <c r="H362" s="4" t="inlineStr"/>
+      <c r="H362" s="4" t="inlineStr">
+        <is>
+          <t>Утверждённая программа ПЭК и ежегодные отчёты. Все измерения выполнены согласно утвержденного графика, протоколы — в четко установленный срок.</t>
+        </is>
+      </c>
       <c r="I362" s="4" t="inlineStr"/>
-      <c r="J362" s="4" t="inlineStr"/>
+      <c r="J362" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
@@ -12423,14 +12575,22 @@
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
-          <t>Разработка программы ПЭК под структуру площадки</t>
+          <t>Разработка программы ПЭК для предприятия</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr"/>
       <c r="G363" s="4" t="inlineStr"/>
-      <c r="H363" s="4" t="inlineStr"/>
+      <c r="H363" s="4" t="inlineStr">
+        <is>
+          <t>Разработка программы ПЭК для предприятия</t>
+        </is>
+      </c>
       <c r="I363" s="4" t="inlineStr"/>
-      <c r="J363" s="4" t="inlineStr"/>
+      <c r="J363" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
@@ -12455,14 +12615,22 @@
       </c>
       <c r="E364" s="4" t="inlineStr">
         <is>
-          <t>План-график измерений по средам и точкам контроля</t>
+          <t>Согласование сроков проведения контроля на предприятии с лабораторией</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr"/>
       <c r="G364" s="4" t="inlineStr"/>
-      <c r="H364" s="4" t="inlineStr"/>
+      <c r="H364" s="4" t="inlineStr">
+        <is>
+          <t>согласование сроков проведения контроля на предприятии с лабораторией</t>
+        </is>
+      </c>
       <c r="I364" s="4" t="inlineStr"/>
-      <c r="J364" s="4" t="inlineStr"/>
+      <c r="J364" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
@@ -12487,14 +12655,22 @@
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
-          <t>Инструментальные измерения «Аналитик Лаб»</t>
+          <t>Инструментальные измерения ООО «Аналитик Лаб»</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr"/>
       <c r="G365" s="4" t="inlineStr"/>
-      <c r="H365" s="4" t="inlineStr"/>
+      <c r="H365" s="4" t="inlineStr">
+        <is>
+          <t>Инструментальные измерения ООО «Аналитик Лаб»</t>
+        </is>
+      </c>
       <c r="I365" s="4" t="inlineStr"/>
-      <c r="J365" s="4" t="inlineStr"/>
+      <c r="J365" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
@@ -12551,14 +12727,22 @@
       </c>
       <c r="E367" s="4" t="inlineStr">
         <is>
-          <t>Корректировка программы при изменениях на объекте</t>
+          <t>Корректировка программы ПЭК при изменениях технологических процессов на объекте</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr"/>
       <c r="G367" s="4" t="inlineStr"/>
-      <c r="H367" s="4" t="inlineStr"/>
+      <c r="H367" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корректировка программы ПЭК при изменениях технологических процессов на объекте </t>
+        </is>
+      </c>
       <c r="I367" s="4" t="inlineStr"/>
-      <c r="J367" s="4" t="inlineStr"/>
+      <c r="J367" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
@@ -12903,14 +13087,22 @@
       </c>
       <c r="E378" s="4" t="inlineStr">
         <is>
-          <t>Оценка воздействия на период строительства и эксплуатации</t>
+          <t>Оценка воздействия проектируемого объекта на период строительства и эксплуатации на все компоненты окружающей среды</t>
         </is>
       </c>
       <c r="F378" s="4" t="inlineStr"/>
       <c r="G378" s="4" t="inlineStr"/>
-      <c r="H378" s="4" t="inlineStr"/>
+      <c r="H378" s="4" t="inlineStr">
+        <is>
+          <t>Оценка воздействия проектируемого объекта на период строительства и эксплуатации  на все компоненты окружающей среды</t>
+        </is>
+      </c>
       <c r="I378" s="4" t="inlineStr"/>
-      <c r="J378" s="4" t="inlineStr"/>
+      <c r="J378" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
@@ -12935,14 +13127,22 @@
       </c>
       <c r="E379" s="4" t="inlineStr">
         <is>
-          <t>Расчёты выбросов, сбросов и образования отходов</t>
+          <t>[удалено]</t>
         </is>
       </c>
       <c r="F379" s="4" t="inlineStr"/>
       <c r="G379" s="4" t="inlineStr"/>
-      <c r="H379" s="4" t="inlineStr"/>
+      <c r="H379" s="4" t="inlineStr">
+        <is>
+          <t>удалить</t>
+        </is>
+      </c>
       <c r="I379" s="4" t="inlineStr"/>
-      <c r="J379" s="4" t="inlineStr"/>
+      <c r="J379" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
@@ -12967,14 +13167,22 @@
       </c>
       <c r="E380" s="4" t="inlineStr">
         <is>
-          <t>Разработка природоохранных мероприятий</t>
+          <t>Разработка комплекса природоохранных мероприятий, направленных на сохранение компонентов окружающей среды</t>
         </is>
       </c>
       <c r="F380" s="4" t="inlineStr"/>
       <c r="G380" s="4" t="inlineStr"/>
-      <c r="H380" s="4" t="inlineStr"/>
+      <c r="H380" s="4" t="inlineStr">
+        <is>
+          <t>Разработка комплекса природоохранных мероприятий, направленных на сохранение компонетов окружающей среды</t>
+        </is>
+      </c>
       <c r="I380" s="4" t="inlineStr"/>
-      <c r="J380" s="4" t="inlineStr"/>
+      <c r="J380" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
@@ -12999,14 +13207,22 @@
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
-          <t>Расчёт затрат на охрану окружающей среды</t>
+          <t>Расчёт стоимости природоохранных мероприятий на период строительства и эксплуатации проектируемого объекта</t>
         </is>
       </c>
       <c r="F381" s="4" t="inlineStr"/>
       <c r="G381" s="4" t="inlineStr"/>
-      <c r="H381" s="4" t="inlineStr"/>
+      <c r="H381" s="4" t="inlineStr">
+        <is>
+          <t>Расчет стоимость природоохранных мероприятий на период строительства и эксплуатации проектируемого объекта</t>
+        </is>
+      </c>
       <c r="I381" s="4" t="inlineStr"/>
-      <c r="J381" s="4" t="inlineStr"/>
+      <c r="J381" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
@@ -13415,14 +13631,22 @@
       </c>
       <c r="E394" s="4" t="inlineStr">
         <is>
-          <t>Расчёты по выбросам, сбросам и отходам</t>
+          <t>[удалено]</t>
         </is>
       </c>
       <c r="F394" s="4" t="inlineStr"/>
       <c r="G394" s="4" t="inlineStr"/>
-      <c r="H394" s="4" t="inlineStr"/>
+      <c r="H394" s="4" t="inlineStr">
+        <is>
+          <t>удалить</t>
+        </is>
+      </c>
       <c r="I394" s="4" t="inlineStr"/>
-      <c r="J394" s="4" t="inlineStr"/>
+      <c r="J394" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
@@ -13447,14 +13671,22 @@
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
-          <t>Формирование декларации и приложений</t>
+          <t>Формирование декларации в личном кабинете природопользователя и её подача</t>
         </is>
       </c>
       <c r="F395" s="4" t="inlineStr"/>
       <c r="G395" s="4" t="inlineStr"/>
-      <c r="H395" s="4" t="inlineStr"/>
+      <c r="H395" s="4" t="inlineStr">
+        <is>
+          <t>Формирование декларации в личном кабинете природопользователя и ее подача</t>
+        </is>
+      </c>
       <c r="I395" s="4" t="inlineStr"/>
-      <c r="J395" s="4" t="inlineStr"/>
+      <c r="J395" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
@@ -13479,14 +13711,22 @@
       </c>
       <c r="E396" s="4" t="inlineStr">
         <is>
-          <t>Подача через личный кабинет природопользователя</t>
+          <t>[удалено]</t>
         </is>
       </c>
       <c r="F396" s="4" t="inlineStr"/>
       <c r="G396" s="4" t="inlineStr"/>
-      <c r="H396" s="4" t="inlineStr"/>
+      <c r="H396" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">удалить </t>
+        </is>
+      </c>
       <c r="I396" s="4" t="inlineStr"/>
-      <c r="J396" s="4" t="inlineStr"/>
+      <c r="J396" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
@@ -13831,14 +14071,22 @@
       </c>
       <c r="E407" s="4" t="inlineStr">
         <is>
-          <t>Все экологические обязательства закрыты вовремя. Дешевле штатной единицы, надёжнее разовых подрядчиков.</t>
+          <t>Соблюдение предприятием всех требований природоохранного законодательства.</t>
         </is>
       </c>
       <c r="F407" s="4" t="inlineStr"/>
       <c r="G407" s="4" t="inlineStr"/>
-      <c r="H407" s="4" t="inlineStr"/>
+      <c r="H407" s="4" t="inlineStr">
+        <is>
+          <t>Соблюдение придпритием всех требований природоохранного законадательства</t>
+        </is>
+      </c>
       <c r="I407" s="4" t="inlineStr"/>
-      <c r="J407" s="4" t="inlineStr"/>
+      <c r="J407" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
@@ -13863,14 +14111,22 @@
       </c>
       <c r="E408" s="4" t="inlineStr">
         <is>
-          <t>Аудит текущего состояния и реестр обязательств</t>
+          <t>Выездной аудит деятельности предприятия в части соблюдения требований действующего законодательства</t>
         </is>
       </c>
       <c r="F408" s="4" t="inlineStr"/>
       <c r="G408" s="4" t="inlineStr"/>
-      <c r="H408" s="4" t="inlineStr"/>
+      <c r="H408" s="4" t="inlineStr">
+        <is>
+          <t>Выездной аудит деятельности предприятия в части соблюдения требований действующего законодательства</t>
+        </is>
+      </c>
       <c r="I408" s="4" t="inlineStr"/>
-      <c r="J408" s="4" t="inlineStr"/>
+      <c r="J408" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
@@ -13895,14 +14151,22 @@
       </c>
       <c r="E409" s="4" t="inlineStr">
         <is>
-          <t>Календарь отчётности и контроль сроков</t>
+          <t>Составление пакета необходимой документации в части соблюдения требований природоохранного законодательства в зависимости от деятельности предприятия</t>
         </is>
       </c>
       <c r="F409" s="4" t="inlineStr"/>
       <c r="G409" s="4" t="inlineStr"/>
-      <c r="H409" s="4" t="inlineStr"/>
+      <c r="H409" s="4" t="inlineStr">
+        <is>
+          <t>Составление пакета необъодимой документации в части соблюдения требований природоохранного законадательства в зависимости от деятельности предприятия</t>
+        </is>
+      </c>
       <c r="I409" s="4" t="inlineStr"/>
-      <c r="J409" s="4" t="inlineStr"/>
+      <c r="J409" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
@@ -13959,14 +14223,22 @@
       </c>
       <c r="E411" s="4" t="inlineStr">
         <is>
-          <t>Подготовка и сдача всей текущей отчётности</t>
+          <t>Подготовка и сдача всей текущей отчётности в срок</t>
         </is>
       </c>
       <c r="F411" s="4" t="inlineStr"/>
       <c r="G411" s="4" t="inlineStr"/>
-      <c r="H411" s="4" t="inlineStr"/>
+      <c r="H411" s="4" t="inlineStr">
+        <is>
+          <t>Подготовка и сдача всей текущей отчётности в срок</t>
+        </is>
+      </c>
       <c r="I411" s="4" t="inlineStr"/>
-      <c r="J411" s="4" t="inlineStr"/>
+      <c r="J411" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
@@ -13991,14 +14263,22 @@
       </c>
       <c r="E412" s="4" t="inlineStr">
         <is>
-          <t>Сопровождение проверок и ответов на запросы</t>
+          <t>Сопровождение проверок и ответов на запросы надзорных органов</t>
         </is>
       </c>
       <c r="F412" s="4" t="inlineStr"/>
       <c r="G412" s="4" t="inlineStr"/>
-      <c r="H412" s="4" t="inlineStr"/>
+      <c r="H412" s="4" t="inlineStr">
+        <is>
+          <t>Сопровождение проверок и ответов на запросы надзорных органов</t>
+        </is>
+      </c>
       <c r="I412" s="4" t="inlineStr"/>
-      <c r="J412" s="4" t="inlineStr"/>
+      <c r="J412" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
@@ -14279,14 +14559,22 @@
       </c>
       <c r="E421" s="4" t="inlineStr">
         <is>
-          <t>респонденты статнаблюдения</t>
+          <t>действующие предприятия</t>
         </is>
       </c>
       <c r="F421" s="4" t="inlineStr"/>
       <c r="G421" s="4" t="inlineStr"/>
-      <c r="H421" s="4" t="inlineStr"/>
+      <c r="H421" s="4" t="inlineStr">
+        <is>
+          <t>действующие предприятия</t>
+        </is>
+      </c>
       <c r="I421" s="4" t="inlineStr"/>
-      <c r="J421" s="4" t="inlineStr"/>
+      <c r="J421" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
@@ -14343,14 +14631,22 @@
       </c>
       <c r="E423" s="4" t="inlineStr">
         <is>
-          <t>Сбор и проверка исходных данных за отчётный год</t>
+          <t>Сбор и проверка исходных данных за отчётный период</t>
         </is>
       </c>
       <c r="F423" s="4" t="inlineStr"/>
       <c r="G423" s="4" t="inlineStr"/>
-      <c r="H423" s="4" t="inlineStr"/>
+      <c r="H423" s="4" t="inlineStr">
+        <is>
+          <t>Сбор и проверка исходных данных за отчётный период</t>
+        </is>
+      </c>
       <c r="I423" s="4" t="inlineStr"/>
-      <c r="J423" s="4" t="inlineStr"/>
+      <c r="J423" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
@@ -14439,14 +14735,22 @@
       </c>
       <c r="E426" s="4" t="inlineStr">
         <is>
-          <t>Сдача через личный кабинет природопользователя</t>
+          <t>Подача отчётности через личный кабинет природопользователя</t>
         </is>
       </c>
       <c r="F426" s="4" t="inlineStr"/>
       <c r="G426" s="4" t="inlineStr"/>
-      <c r="H426" s="4" t="inlineStr"/>
+      <c r="H426" s="4" t="inlineStr">
+        <is>
+          <t>Подача отчетности через личный кабинет природопользователя</t>
+        </is>
+      </c>
       <c r="I426" s="4" t="inlineStr"/>
-      <c r="J426" s="4" t="inlineStr"/>
+      <c r="J426" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
@@ -14471,14 +14775,22 @@
       </c>
       <c r="E427" s="4" t="inlineStr">
         <is>
-          <t>Ответы на вопросы принимающих органов</t>
+          <t>Ответы на вопросы надзорных органов</t>
         </is>
       </c>
       <c r="F427" s="4" t="inlineStr"/>
       <c r="G427" s="4" t="inlineStr"/>
-      <c r="H427" s="4" t="inlineStr"/>
+      <c r="H427" s="4" t="inlineStr">
+        <is>
+          <t>Ответы на вопросы надзорных органов</t>
+        </is>
+      </c>
       <c r="I427" s="4" t="inlineStr"/>
-      <c r="J427" s="4" t="inlineStr"/>
+      <c r="J427" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
@@ -14919,14 +15231,22 @@
       </c>
       <c r="E441" s="4" t="inlineStr">
         <is>
-          <t>Актуализация сведений при изменениях</t>
+          <t>Актуализация сведений при изменениях технологических процессов</t>
         </is>
       </c>
       <c r="F441" s="4" t="inlineStr"/>
       <c r="G441" s="4" t="inlineStr"/>
-      <c r="H441" s="4" t="inlineStr"/>
+      <c r="H441" s="4" t="inlineStr">
+        <is>
+          <t>Актуализация сведений при изменениях технилогических процессов</t>
+        </is>
+      </c>
       <c r="I441" s="4" t="inlineStr"/>
-      <c r="J441" s="4" t="inlineStr"/>
+      <c r="J441" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
@@ -15239,14 +15559,22 @@
       </c>
       <c r="E451" s="4" t="inlineStr">
         <is>
-          <t>плательщики платы за НВОС</t>
+          <t>предприятия, имеющие объекты негативного воздействия на окружающую среду</t>
         </is>
       </c>
       <c r="F451" s="4" t="inlineStr"/>
       <c r="G451" s="4" t="inlineStr"/>
-      <c r="H451" s="4" t="inlineStr"/>
+      <c r="H451" s="4" t="inlineStr">
+        <is>
+          <t>предприятия имеющие объекта негативного воздействия на окружающую среду</t>
+        </is>
+      </c>
       <c r="I451" s="4" t="inlineStr"/>
-      <c r="J451" s="4" t="inlineStr"/>
+      <c r="J451" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
@@ -15303,14 +15631,22 @@
       </c>
       <c r="E453" s="4" t="inlineStr">
         <is>
-          <t>Проверка применяемых ставок и коэффициентов</t>
+          <t>Анализ деятельности предприятия и наличия природоохранной документации</t>
         </is>
       </c>
       <c r="F453" s="4" t="inlineStr"/>
       <c r="G453" s="4" t="inlineStr"/>
-      <c r="H453" s="4" t="inlineStr"/>
+      <c r="H453" s="4" t="inlineStr">
+        <is>
+          <t>Анализ деятельности предприятия и наличие природоохранной документации</t>
+        </is>
+      </c>
       <c r="I453" s="4" t="inlineStr"/>
-      <c r="J453" s="4" t="inlineStr"/>
+      <c r="J453" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
@@ -15783,14 +16119,22 @@
       </c>
       <c r="E468" s="4" t="inlineStr">
         <is>
-          <t>Программа изысканий под задачи проекта</t>
+          <t>Составление программы изысканий под задачи проекта</t>
         </is>
       </c>
       <c r="F468" s="4" t="inlineStr"/>
       <c r="G468" s="4" t="inlineStr"/>
-      <c r="H468" s="4" t="inlineStr"/>
+      <c r="H468" s="4" t="inlineStr">
+        <is>
+          <t>Составление программы изысканий под задачи проекта</t>
+        </is>
+      </c>
       <c r="I468" s="4" t="inlineStr"/>
-      <c r="J468" s="4" t="inlineStr"/>
+      <c r="J468" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
@@ -15911,14 +16255,22 @@
       </c>
       <c r="E472" s="4" t="inlineStr">
         <is>
-          <t>Технический отчёт для экспертизы любого уровня</t>
+          <t>Разработка технического отчёта по результатам проведённых исследований</t>
         </is>
       </c>
       <c r="F472" s="4" t="inlineStr"/>
       <c r="G472" s="4" t="inlineStr"/>
-      <c r="H472" s="4" t="inlineStr"/>
+      <c r="H472" s="4" t="inlineStr">
+        <is>
+          <t>Разработка технического отчёта по результатам проведенных исследований</t>
+        </is>
+      </c>
       <c r="I472" s="4" t="inlineStr"/>
-      <c r="J472" s="4" t="inlineStr"/>
+      <c r="J472" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
@@ -16807,14 +17159,22 @@
       </c>
       <c r="E500" s="4" t="inlineStr">
         <is>
-          <t>Инструментальный контроль промышленных выбросов</t>
+          <t>Оценка атмосферного воздуха по физическим факторам</t>
         </is>
       </c>
       <c r="F500" s="4" t="inlineStr"/>
       <c r="G500" s="4" t="inlineStr"/>
-      <c r="H500" s="4" t="inlineStr"/>
+      <c r="H500" s="4" t="inlineStr">
+        <is>
+          <t>Оценка атмосферного воздуха по физическим факторам</t>
+        </is>
+      </c>
       <c r="I500" s="4" t="inlineStr"/>
-      <c r="J500" s="4" t="inlineStr"/>
+      <c r="J500" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
@@ -16839,14 +17199,22 @@
       </c>
       <c r="E501" s="4" t="inlineStr">
         <is>
-          <t>Метеонаблюдения при отборе проб</t>
+          <t>[удалено]</t>
         </is>
       </c>
       <c r="F501" s="4" t="inlineStr"/>
       <c r="G501" s="4" t="inlineStr"/>
-      <c r="H501" s="4" t="inlineStr"/>
+      <c r="H501" s="4" t="inlineStr">
+        <is>
+          <t>удалить</t>
+        </is>
+      </c>
       <c r="I501" s="4" t="inlineStr"/>
-      <c r="J501" s="4" t="inlineStr"/>
+      <c r="J501" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
@@ -16871,14 +17239,22 @@
       </c>
       <c r="E502" s="4" t="inlineStr">
         <is>
-          <t>Протоколы и свод результатов для отчётности</t>
+          <t>Протоколы результатов выполненных исследований</t>
         </is>
       </c>
       <c r="F502" s="4" t="inlineStr"/>
       <c r="G502" s="4" t="inlineStr"/>
-      <c r="H502" s="4" t="inlineStr"/>
+      <c r="H502" s="4" t="inlineStr">
+        <is>
+          <t>Протоколы результатов выполненных исследований</t>
+        </is>
+      </c>
       <c r="I502" s="4" t="inlineStr"/>
-      <c r="J502" s="4" t="inlineStr"/>
+      <c r="J502" s="4" t="inlineStr">
+        <is>
+          <t>Внесено (вычитка 2)</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
